--- a/CASES/Insitu XRD/lattice_results.xlsx
+++ b/CASES/Insitu XRD/lattice_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[  2.86      2.86     14.25673  90.       90.      120.     ]</t>
+          <t>[  2.85413   2.85413  14.17488  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[  2.86033   2.86033  14.2447   90.       90.      120.     ]</t>
+          <t>[  2.85118   2.85118  14.19123  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[  2.84008   2.84008  14.26148  90.       90.      120.     ]</t>
+          <t>[  2.85114   2.85114  14.18145  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[  2.86326   2.86326  14.23535  90.       90.      120.     ]</t>
+          <t>[  2.85151   2.85151  14.1863   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[  2.83444   2.83444  14.31002  90.       90.      120.     ]</t>
+          <t>[  2.8516    2.8516   14.17722  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[  2.85621   2.85621  14.23366  90.       90.      120.     ]</t>
+          <t>[  2.85256   2.85256  14.17807  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[  2.84368   2.84368  14.2464   90.       90.      120.     ]</t>
+          <t>[  2.85163   2.85163  14.1779   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[  2.85681   2.85681  14.23415  90.       90.      120.     ]</t>
+          <t>[  2.85143   2.85143  14.17868  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[  2.84966   2.84966  14.24613  90.       90.      120.     ]</t>
+          <t>[  2.85397   2.85397  14.17031  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[  2.83928   2.83928  14.20077  90.       90.      120.     ]</t>
+          <t>[  2.85618   2.85618  14.16641  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[  2.86763   2.86763  14.22786  90.       90.      120.     ]</t>
+          <t>[  2.85175   2.85175  14.17216  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[  2.85898   2.85898  14.30636  90.       90.      120.     ]</t>
+          <t>[  2.85256   2.85256  14.17384  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[  2.85877   2.85877  14.23316  90.       90.      120.     ]</t>
+          <t>[  2.85164   2.85164  14.1712   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[  2.84733   2.84733  14.27698  90.       90.      120.     ]</t>
+          <t>[  2.8518    2.8518   14.17551  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[  2.85171   2.85171  14.24372  90.       90.      120.     ]</t>
+          <t>[  2.85262   2.85262  14.16347  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[  2.86534   2.86534  14.25356  90.       90.      120.     ]</t>
+          <t>[  2.85103   2.85103  14.17229  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[  2.82983   2.82983  14.31205  90.       90.      120.     ]</t>
+          <t>[  2.84988   2.84988  14.16994  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[  2.81752   2.81752  14.37303  90.       90.      120.     ]</t>
+          <t>[  2.84915   2.84915  14.17152  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[  2.8287    2.8287   14.30415  90.       90.      120.     ]</t>
+          <t>[  2.8477    2.8477   14.16832  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[  2.83624   2.83624  14.25784  90.       90.      120.     ]</t>
+          <t>[  2.85214   2.85214  14.15404  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[  2.83972   2.83972  14.23986  90.       90.      120.     ]</t>
+          <t>[  2.85215   2.85215  14.15741  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[  2.83471   2.83471  14.26079  90.       90.      120.     ]</t>
+          <t>[  2.85174   2.85174  14.15524  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[  2.86536   2.86536  14.22844  90.       90.      120.     ]</t>
+          <t>[  2.8538    2.8538   14.14567  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[  2.82319   2.82319  14.40126  90.       90.      120.     ]</t>
+          <t>[  2.85594   2.85594  14.13536  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -734,11 +734,7 @@
           <t>./data/25.xlsx</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>[  2.84591   2.84591  14.23677  90.       90.      120.     ]</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -748,7 +744,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[  2.84931   2.84931  14.26107  90.       90.      120.     ]</t>
+          <t>[  2.85586   2.85586  14.13843  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -760,7 +756,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[  2.82716   2.82716  14.37847  90.       90.      120.     ]</t>
+          <t>[  2.85777   2.85777  14.13006  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -772,7 +768,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[  2.84558   2.84558  14.27028  90.       90.      120.     ]</t>
+          <t>[  2.85826   2.85826  14.12791  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -784,7 +780,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[  2.86503   2.86503  14.21541  90.       90.      120.     ]</t>
+          <t>[  2.8575   2.8575  14.1349  90.      90.     120.    ]</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[  2.82878   2.82878  14.29164  90.       90.      120.     ]</t>
+          <t>[  2.85749   2.85749  14.12128  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -808,7 +804,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[  2.84496   2.84496  14.26371  90.       90.      120.     ]</t>
+          <t>[  2.85642   2.85642  14.13134  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -820,7 +816,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[  2.82858   2.82858  14.36647  90.       90.      120.     ]</t>
+          <t>[  2.85732   2.85732  14.13057  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -832,7 +828,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[  2.83387   2.83387  14.28448  90.       90.      120.     ]</t>
+          <t>[  2.85785   2.85785  14.12175  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -844,7 +840,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[  2.81292   2.81292  14.40112  90.       90.      120.     ]</t>
+          <t>[  2.85562   2.85562  14.13464  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -856,7 +852,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[  2.81365   2.81365  14.37821  90.       90.      120.     ]</t>
+          <t>[  2.85551   2.85551  14.13598  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -868,7 +864,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[  2.82714   2.82714  14.28159  90.       90.      120.     ]</t>
+          <t>[  2.85509   2.85509  14.14155  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -880,7 +876,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[  2.81634   2.81634  14.30218  90.       90.      120.     ]</t>
+          <t>[  2.85248   2.85248  14.14733  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -892,7 +888,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[  2.82405   2.82405  14.28731  90.       90.      120.     ]</t>
+          <t>[  2.8524    2.8524   14.15083  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -904,7 +900,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[  2.81731   2.81731  14.37536  90.       90.      120.     ]</t>
+          <t>[  2.85285   2.85285  14.1459   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -916,7 +912,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[  2.82883   2.82883  14.2975   90.       90.      120.     ]</t>
+          <t>[  2.8511    2.8511   14.15112  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -928,7 +924,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[  2.82095   2.82095  14.34529  90.       90.      120.     ]</t>
+          <t>[  2.85057   2.85057  14.14939  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -940,7 +936,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[  2.83743   2.83743  14.21344  90.       90.      120.     ]</t>
+          <t>[  2.84419   2.84419  14.14564  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -952,7 +948,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[  2.83508   2.83508  14.23174  90.       90.      120.     ]</t>
+          <t>[  2.84541   2.84541  14.15456  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -964,7 +960,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[  2.83039   2.83039  14.2701   90.       90.      120.     ]</t>
+          <t>[  2.84044   2.84044  14.14754  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -976,7 +972,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[  2.82087   2.82087  14.32711  90.       90.      120.     ]</t>
+          <t>[  2.83725   2.83725  14.15807  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -988,7 +984,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[  2.82463   2.82463  14.30679  90.       90.      120.     ]</t>
+          <t>[  2.83523   2.83523  14.16447  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1000,7 +996,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[  2.85292   2.85292  14.18868  90.       90.      120.     ]</t>
+          <t>[  2.82917   2.82917  14.15881  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1008,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[  2.84756   2.84756  14.16411  90.       90.      120.     ]</t>
+          <t>[  2.82508   2.82508  14.15756  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1020,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[  2.84508   2.84508  14.19003  90.       90.      120.     ]</t>
+          <t>[  2.83104   2.83104  14.15884  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1032,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[  2.83847   2.83847  14.16598  90.       90.      120.     ]</t>
+          <t>[  2.8373    2.8373   14.15047  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1044,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[  2.82646   2.82646  14.33075  90.       90.      120.     ]</t>
+          <t>[  2.85044   2.85044  14.15238  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1056,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[  2.84517   2.84517  14.20841  90.       90.      120.     ]</t>
+          <t>[  2.8499    2.8499   14.14626  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1068,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[  2.82388   2.82388  14.20874  90.       90.      120.     ]</t>
+          <t>[  2.85028   2.85028  14.14537  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[  2.85452   2.85452  14.30384  90.       90.      120.     ]</t>
+          <t>[  2.8498    2.8498   14.16756  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1092,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[  2.82121   2.82121  14.27571  90.       90.      120.     ]</t>
+          <t>[  2.84651   2.84651  14.17541  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[  2.85235   2.85235  14.29843  90.       90.      120.     ]</t>
+          <t>[  2.84722   2.84722  14.17507  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1116,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[  2.85798   2.85798  14.25725  90.       90.      120.     ]</t>
+          <t>[  2.84663   2.84663  14.17695  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1128,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[  2.83746   2.83746  14.21365  90.       90.      120.     ]</t>
+          <t>[  2.84737   2.84737  14.17468  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1140,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[  2.83678   2.83678  14.29082  90.       90.      120.     ]</t>
+          <t>[  2.84682   2.84682  14.17292  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1152,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[  2.86321   2.86321  14.24474  90.       90.      120.     ]</t>
+          <t>[  2.84432   2.84432  14.18382  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1164,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[  2.83962   2.83962  14.25184  90.       90.      120.     ]</t>
+          <t>[  2.84952   2.84952  14.17959  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1176,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[  2.8215    2.8215   14.29339  90.       90.      120.     ]</t>
+          <t>[  2.8505    2.8505   14.17208  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1188,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[  2.84088   2.84088  14.26977  90.       90.      120.     ]</t>
+          <t>[  2.84981   2.84981  14.16557  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1200,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[  2.84546   2.84546  14.21524  90.       90.      120.     ]</t>
+          <t>[  2.84864   2.84864  14.15363  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1212,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[  2.85194   2.85194  14.16095  90.       90.      120.     ]</t>
+          <t>[  2.83874   2.83874  14.16221  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1226,11 +1222,7 @@
           <t>./data/66.xlsx</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>[  2.8791    2.8791   14.15114  90.       90.      120.     ]</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1240,7 +1232,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[  2.85009   2.85009  14.18875  90.       90.      120.     ]</t>
+          <t>[  2.84356   2.84356  14.16035  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1244,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[  2.82443   2.82443  14.287    90.       90.      120.     ]</t>
+          <t>[  2.83815   2.83815  14.15474  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1256,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[  2.93909   2.93909  14.05686  90.       90.      120.     ]</t>
+          <t>[  2.83594   2.83594  14.14442  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1268,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[  2.83171   2.83171  14.2057   90.       90.      120.     ]</t>
+          <t>[  2.84579   2.84579  14.1239   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1280,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[  2.9335    2.9335   14.05706  90.       90.      120.     ]</t>
+          <t>[  2.84583   2.84583  14.12149  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1292,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[  2.82195   2.82195  14.28491  90.       90.      120.     ]</t>
+          <t>[  2.84507   2.84507  14.1118   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1304,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[  2.82404   2.82404  14.20705  90.       90.      120.     ]</t>
+          <t>[  2.8381    2.8381   14.10579  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1316,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[  2.80021   2.80021  14.22293  90.       90.      120.     ]</t>
+          <t>[  2.82584   2.82584  14.10405  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1328,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[  2.94557   2.94557  14.0336   90.       90.      120.     ]</t>
+          <t>[  2.82207   2.82207  14.07931  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1340,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[  2.82704   2.82704  14.12542  90.       90.      120.     ]</t>
+          <t>[  2.82069   2.82069  14.0528   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1352,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[  2.81473   2.81473  14.11307  90.       90.      120.     ]</t>
+          <t>[  2.81581   2.81581  14.04031  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1364,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[  2.79764   2.79764  14.14535  90.       90.      120.     ]</t>
+          <t>[  2.81694   2.81694  14.03217  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1376,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[  2.82556   2.82556  14.09282  90.       90.      120.     ]</t>
+          <t>[  2.81504   2.81504  14.01241  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[  2.79597   2.79597  14.00874  90.       90.      120.     ]</t>
+          <t>[  2.80825   2.80825  14.00692  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1400,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[  2.88637   2.88637  14.02424  90.       90.      120.     ]</t>
+          <t>[  2.80555   2.80555  14.00065  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1412,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[  2.85405   2.85405  14.06501  90.       90.      120.     ]</t>
+          <t>[  2.8029   2.8029  13.9914  90.      90.     120.    ]</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1424,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[  2.90321   2.90321  14.05878  90.       90.      120.     ]</t>
+          <t>[  2.79801   2.79801  13.99432  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1436,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[  2.94451   2.94451  13.96644  90.       90.      120.     ]</t>
+          <t>[  2.79659   2.79659  13.9903   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1448,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[  2.77336   2.77336  14.03826  90.       90.      120.     ]</t>
+          <t>[  2.79678   2.79678  13.98887  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1460,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[  2.94349   2.94349  13.96044  90.       90.      120.     ]</t>
+          <t>[  2.79384   2.79384  13.98808  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1472,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[  2.77393   2.77393  14.14602  90.       90.      120.     ]</t>
+          <t>[  2.78969   2.78969  13.98261  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1484,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[  2.88368   2.88368  13.99353  90.       90.      120.     ]</t>
+          <t>[  2.78125   2.78125  13.99537  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1496,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[  2.93498   2.93498  13.94697  90.       90.      120.     ]</t>
+          <t>[  2.78164   2.78164  13.97971  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1508,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[  2.90104   2.90104  13.99553  90.       90.      120.     ]</t>
+          <t>[  2.78085   2.78085  13.97226  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1520,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[  2.91292   2.91292  13.99967  90.       90.      120.     ]</t>
+          <t>[  2.77771   2.77771  13.95798  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1532,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[  2.77484   2.77484  13.97459  90.       90.      120.     ]</t>
+          <t>[  2.78319   2.78319  13.94602  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1544,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[  2.95114   2.95114  13.93185  90.       90.      120.     ]</t>
+          <t>[  2.78636   2.78636  13.95049  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1562,11 +1554,7 @@
           <t>./data/94.xlsx</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>[  2.77778   2.77778  14.04742  90.       90.      120.     ]</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1576,7 +1564,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[  2.82644   2.82644  14.06725  90.       90.      120.     ]</t>
+          <t>[  2.78358   2.78358  13.95559  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1576,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[  2.78046   2.78046  14.06294  90.       90.      120.     ]</t>
+          <t>[  2.78202   2.78202  13.97822  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1588,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[  2.79606   2.79606  14.1088   90.       90.      120.     ]</t>
+          <t>[  2.78469   2.78469  13.97309  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1600,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[  2.93612   2.93612  13.98572  90.       90.      120.     ]</t>
+          <t>[  2.78235   2.78235  13.95861  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1612,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[  2.82912   2.82912  14.18124  90.       90.      120.     ]</t>
+          <t>[  2.77908   2.77908  14.00005  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1624,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[  2.82418   2.82418  14.18713  90.       90.      120.     ]</t>
+          <t>[  2.78219   2.78219  13.98454  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1636,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[  2.81218   2.81218  14.1285   90.       90.      120.     ]</t>
+          <t>[  2.76076   2.76076  14.04468  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1648,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[  2.83273   2.83273  14.17114  90.       90.      120.     ]</t>
+          <t>[  2.75834   2.75834  14.07489  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1660,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[  2.8317    2.8317   14.21981  90.       90.      120.     ]</t>
+          <t>[  2.76511   2.76511  14.10292  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1672,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[  2.89962   2.89962  14.12465  90.       90.      120.     ]</t>
+          <t>[  2.76705   2.76705  14.10177  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1684,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[  2.80967   2.80967  14.34017  90.       90.      120.     ]</t>
+          <t>[  2.76975   2.76975  14.11686  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1696,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[  2.83593   2.83593  14.22383  90.       90.      120.     ]</t>
+          <t>[  2.77005   2.77005  14.11192  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1708,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[  2.88138   2.88138  14.15577  90.       90.      120.     ]</t>
+          <t>[  2.76758   2.76758  14.10477  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1720,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[  2.88899   2.88899  14.13009  90.       90.      120.     ]</t>
+          <t>[  2.77008   2.77008  14.07909  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1732,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[  2.85895   2.85895  14.12423  90.       90.      120.     ]</t>
+          <t>[  2.7703    2.7703   14.10201  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1742,7 @@
           <t>./data/110.xlsx</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>[  2.83601   2.83601  14.25918  90.       90.      120.     ]</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[  2.83253   2.83253  14.24622  90.       90.      120.     ]</t>
+          <t>[  2.7685    2.7685   14.14008  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1764,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[  2.82106   2.82106  14.27276  90.       90.      120.     ]</t>
+          <t>[  2.77075   2.77075  14.1488   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1776,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[  2.82284   2.82284  14.30193  90.       90.      120.     ]</t>
+          <t>[  2.77293   2.77293  14.153    90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1788,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[  2.83137   2.83137  14.31618  90.       90.      120.     ]</t>
+          <t>[  2.77106   2.77106  14.15947  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1800,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[  2.84654   2.84654  14.19083  90.       90.      120.     ]</t>
+          <t>[  2.77304   2.77304  14.16197  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1812,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[  2.82079   2.82079  14.26295  90.       90.      120.     ]</t>
+          <t>[  2.77539   2.77539  14.16003  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1824,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[  2.83482   2.83482  14.27274  90.       90.      120.     ]</t>
+          <t>[  2.77233   2.77233  14.15418  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1836,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[  2.85284   2.85284  14.23809  90.       90.      120.     ]</t>
+          <t>[  2.77218   2.77218  14.15848  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1848,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[  2.82412   2.82412  14.1766   90.       90.      120.     ]</t>
+          <t>[  2.77501   2.77501  14.15346  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1860,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[  2.82702   2.82702  14.21113  90.       90.      120.     ]</t>
+          <t>[  2.77397   2.77397  14.15284  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1872,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[  2.81963   2.81963  14.29986  90.       90.      120.     ]</t>
+          <t>[  2.77482   2.77482  14.15321  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1884,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[  2.83865   2.83865  14.30989  90.       90.      120.     ]</t>
+          <t>[  2.77306   2.77306  14.15005  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1896,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>[  2.82203   2.82203  14.32351  90.       90.      120.     ]</t>
+          <t>[  2.77121   2.77121  14.14534  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1908,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[  2.82546   2.82546  14.30107  90.       90.      120.     ]</t>
+          <t>[  2.77272   2.77272  14.14013  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1920,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[  2.8254   2.8254  14.3154  90.      90.     120.    ]</t>
+          <t>[  2.76978   2.76978  14.15582  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1932,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[  2.82826   2.82826  14.30241  90.       90.      120.     ]</t>
+          <t>[  2.77987   2.77987  14.15061  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1944,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[  2.82517   2.82517  14.328    90.       90.      120.     ]</t>
+          <t>[  2.78039   2.78039  14.14861  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1956,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[  2.83202   2.83202  14.21907  90.       90.      120.     ]</t>
+          <t>[  2.78332   2.78332  14.14612  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1968,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[  2.84769   2.84769  14.23077  90.       90.      120.     ]</t>
+          <t>[  2.78581   2.78581  14.14567  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1980,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[  2.82796   2.82796  14.34731  90.       90.      120.     ]</t>
+          <t>[  2.79008   2.79008  14.14894  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2008,7 +1992,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[  2.87334   2.87334  14.21845  90.       90.      120.     ]</t>
+          <t>[  2.78729   2.78729  14.14651  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2004,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[  2.82763   2.82763  14.30184  90.       90.      120.     ]</t>
+          <t>[  2.78379   2.78379  14.14245  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2016,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[  2.82513   2.82513  14.36255  90.       90.      120.     ]</t>
+          <t>[  2.78124   2.78124  14.14936  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2028,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[  2.82749   2.82749  14.36202  90.       90.      120.     ]</t>
+          <t>[  2.77906   2.77906  14.14794  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2040,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[  2.83703   2.83703  14.26446  90.       90.      120.     ]</t>
+          <t>[  2.77585   2.77585  14.13692  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2052,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[  2.8498    2.8498   14.25607  90.       90.      120.     ]</t>
+          <t>[  2.77215   2.77215  14.13349  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2064,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[  2.8353    2.8353   14.27042  90.       90.      120.     ]</t>
+          <t>[  2.76653   2.76653  14.13601  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2076,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[  2.84644   2.84644  14.24403  90.       90.      120.     ]</t>
+          <t>[  2.76453   2.76453  14.14063  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2088,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[  2.85013   2.85013  14.25011  90.       90.      120.     ]</t>
+          <t>[  2.76408   2.76408  14.14052  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2100,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[  2.83492   2.83492  14.25039  90.       90.      120.     ]</t>
+          <t>[  2.77121   2.77121  14.15315  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2112,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[  2.83802   2.83802  14.24399  90.       90.      120.     ]</t>
+          <t>[  2.76372   2.76372  14.15498  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2124,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[  2.83777   2.83777  14.26071  90.       90.      120.     ]</t>
+          <t>[  2.77086   2.77086  14.13088  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2136,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[  2.83728   2.83728  14.26765  90.       90.      120.     ]</t>
+          <t>[  2.77161   2.77161  14.11327  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2148,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[  2.82833   2.82833  14.37944  90.       90.      120.     ]</t>
+          <t>[  2.76622   2.76622  14.11953  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2160,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[  2.84128   2.84128  14.2336   90.       90.      120.     ]</t>
+          <t>[  2.76543   2.76543  14.12255  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2172,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[  2.84016   2.84016  14.24274  90.       90.      120.     ]</t>
+          <t>[  2.76294   2.76294  14.11486  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2184,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[  2.83559   2.83559  14.20732  90.       90.      120.     ]</t>
+          <t>[  2.76431   2.76431  14.1201   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2196,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[  2.85679   2.85679  14.23251  90.       90.      120.     ]</t>
+          <t>[  2.77147   2.77147  14.11596  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2208,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[  2.85695   2.85695  14.23427  90.       90.      120.     ]</t>
+          <t>[  2.78338   2.78338  14.1315   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2218,11 @@
           <t>./data/150.xlsx</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>[  2.79421   2.79421  14.11254  90.       90.      120.     ]</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2244,7 +2232,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[  2.86654   2.86654  14.21965  90.       90.      120.     ]</t>
+          <t>[  2.80833   2.80833  14.11098  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2244,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[  2.82095   2.82095  14.34015  90.       90.      120.     ]</t>
+          <t>[  2.80738   2.80738  14.11389  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2256,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[  2.84178   2.84178  14.24738  90.       90.      120.     ]</t>
+          <t>[  2.80594   2.80594  14.12129  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2278,11 +2266,7 @@
           <t>./data/154.xlsx</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>[  2.8207    2.8207   14.41132  90.       90.      120.     ]</t>
-        </is>
-      </c>
+      <c r="B155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2292,7 +2276,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[  2.85426   2.85426  14.23874  90.       90.      120.     ]</t>
+          <t>[  2.80438   2.80438  14.10849  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2288,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[  2.83577   2.83577  14.25895  90.       90.      120.     ]</t>
+          <t>[  2.8051    2.8051   14.11515  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>

--- a/CASES/Insitu XRD/lattice_results.xlsx
+++ b/CASES/Insitu XRD/lattice_results.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[  2.85413   2.85413  14.17488  90.       90.      120.     ]</t>
+          <t>[  2.86929   2.86929  14.03203  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[  2.85118   2.85118  14.19123  90.       90.      120.     ]</t>
+          <t>[  2.86165   2.86165  14.06046  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[  2.85114   2.85114  14.18145  90.       90.      120.     ]</t>
+          <t>[  2.85818   2.85818  14.04498  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[  2.85151   2.85151  14.1863   90.       90.      120.     ]</t>
+          <t>[  2.8527    2.8527   14.06521  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[  2.8516    2.8516   14.17722  90.       90.      120.     ]</t>
+          <t>[  2.85653   2.85653  14.06203  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[  2.85256   2.85256  14.17807  90.       90.      120.     ]</t>
+          <t>[  2.84975   2.84975  14.08778  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[  2.85163   2.85163  14.1779   90.       90.      120.     ]</t>
+          <t>[  2.85307   2.85307  14.10868  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[  2.85143   2.85143  14.17868  90.       90.      120.     ]</t>
+          <t>[  2.85245   2.85245  14.11186  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[  2.85397   2.85397  14.17031  90.       90.      120.     ]</t>
+          <t>[  2.85857   2.85857  14.12342  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[  2.85618   2.85618  14.16641  90.       90.      120.     ]</t>
+          <t>[  2.85814   2.85814  14.12395  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[  2.85175   2.85175  14.17216  90.       90.      120.     ]</t>
+          <t>[  2.85865   2.85865  14.12519  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[  2.85256   2.85256  14.17384  90.       90.      120.     ]</t>
+          <t>[  2.86009   2.86009  14.12668  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[  2.85164   2.85164  14.1712   90.       90.      120.     ]</t>
+          <t>[  2.85964   2.85964  14.12541  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[  2.8518    2.8518   14.17551  90.       90.      120.     ]</t>
+          <t>[  2.85933   2.85933  14.12173  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[  2.85262   2.85262  14.16347  90.       90.      120.     ]</t>
+          <t>[  2.85952   2.85952  14.1239   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[  2.85103   2.85103  14.17229  90.       90.      120.     ]</t>
+          <t>[  2.85807   2.85807  14.1218   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[  2.84988   2.84988  14.16994  90.       90.      120.     ]</t>
+          <t>[  2.85883   2.85883  14.12559  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[  2.84915   2.84915  14.17152  90.       90.      120.     ]</t>
+          <t>[  2.85856   2.85856  14.12454  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[  2.8477    2.8477   14.16832  90.       90.      120.     ]</t>
+          <t>[  2.85813   2.85813  14.12675  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[  2.85214   2.85214  14.15404  90.       90.      120.     ]</t>
+          <t>[  2.8586    2.8586   14.12704  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[  2.85215   2.85215  14.15741  90.       90.      120.     ]</t>
+          <t>[  2.85745   2.85745  14.12966  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[  2.85174   2.85174  14.15524  90.       90.      120.     ]</t>
+          <t>[  2.85767   2.85767  14.1268   90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[  2.8538    2.8538   14.14567  90.       90.      120.     ]</t>
+          <t>[  2.85804   2.85804  14.12987  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[  2.85594   2.85594  14.13536  90.       90.      120.     ]</t>
+          <t>[  2.85698   2.85698  14.13126  90.       90.      120.     ]</t>
         </is>
       </c>
     </row>
